--- a/data/trans_dic/P13A_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,13</t>
+          <t>1,09; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,67</t>
+          <t>4,45; 8,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,84</t>
+          <t>3,26; 5,65</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,71</t>
+          <t>0,65; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,54</t>
+          <t>2,59; 4,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,85</t>
+          <t>1,8; 2,85</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,62</t>
+          <t>1,93; 4,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,5</t>
+          <t>1,13; 2,42</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,55</t>
+          <t>0,78; 1,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,77</t>
+          <t>3,19; 4,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,99</t>
+          <t>2,14; 3,01</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5430; 16101</t>
+          <t>5595; 16416</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33433; 65152</t>
+          <t>33416; 63124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42123; 73912</t>
+          <t>41280; 71510</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15778; 39038</t>
+          <t>14825; 38090</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60081; 101318</t>
+          <t>57787; 102092</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81458; 128576</t>
+          <t>81287; 128549</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8290</t>
+          <t>0; 9076</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13305; 30456</t>
+          <t>12691; 28903</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15643; 32573</t>
+          <t>14749; 31510</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26150; 53199</t>
+          <t>26768; 51706</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117053; 173463</t>
+          <t>116173; 172154</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151023; 211515</t>
+          <t>151506; 213357</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13A_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,19</t>
+          <t>0,99; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,4</t>
+          <t>4,03; 6,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,65</t>
+          <t>3,02; 4,69</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,67</t>
+          <t>0,8; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,58</t>
+          <t>3,4; 4,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,85</t>
+          <t>2,2; 3,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,39</t>
+          <t>2,18; 4,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,42</t>
+          <t>1,22; 2,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,5</t>
+          <t>0,81; 1,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,73</t>
+          <t>3,66; 4,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,01</t>
+          <t>2,34; 3,04</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>53192</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5595; 16416</t>
+          <t>5742; 18369</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33416; 63124</t>
+          <t>32908; 53372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41280; 71510</t>
+          <t>42131; 65409</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79975</t>
+          <t>87561</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105347</t>
+          <t>114888</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14825; 38090</t>
+          <t>17768; 41138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57787; 102092</t>
+          <t>73419; 107075</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81287; 128549</t>
+          <t>96167; 137873</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>26240</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9076</t>
+          <t>0; 7312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12691; 28903</t>
+          <t>15960; 35432</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14749; 31510</t>
+          <t>17672; 37316</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>142903</t>
+          <t>154412</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180297</t>
+          <t>194320</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26768; 51706</t>
+          <t>28423; 54866</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116173; 172154</t>
+          <t>135656; 181890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151506; 213357</t>
+          <t>168556; 219230</t>
         </is>
       </c>
     </row>
